--- a/dcf/ESTC.xlsx
+++ b/dcf/ESTC.xlsx
@@ -361,87 +361,87 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 19.9x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -877,7 +877,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1132,184 +1132,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>16.9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>34.91455665609995</v>
+        <v>51.49410078173313</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>33.75910655948027</v>
+        <v>49.57908286094796</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>32.65850121728511</v>
+        <v>47.75701288437452</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>31.60984785843488</v>
+        <v>46.0229223937237</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>30.61042007935013</v>
+        <v>44.37213123952115</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>29.65764752285346</v>
+        <v>42.80022958003478</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>28.74910624263871</v>
+        <v>41.30306108168243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>17.9</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>37.01323312769909</v>
+        <v>53.59277725333227</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>35.76163520523567</v>
+        <v>51.58161150670337</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>34.56970522577743</v>
+        <v>49.66821689286684</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>33.43428767302841</v>
+        <v>47.84736220831721</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>32.35240883380216</v>
+        <v>46.11411999397318</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>31.32126550477515</v>
+        <v>44.46384756195648</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>30.33821445011261</v>
+        <v>42.89216928915631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>18.9</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>39.11190959929822</v>
+        <v>55.69145372493141</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>37.76416385099107</v>
+        <v>53.58414015245878</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>36.48090923426977</v>
+        <v>51.57942090135918</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>35.25872748762193</v>
+        <v>49.67180202291074</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>34.09439758825419</v>
+        <v>47.85610874842521</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>32.98488348669683</v>
+        <v>46.12746554387817</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>31.92732265758649</v>
+        <v>44.48127749663021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>19.9</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>41.21058607089736</v>
+        <v>57.79013019653055</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>39.76669249674648</v>
+        <v>55.58666879821419</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>38.39211324276209</v>
+        <v>53.4906249098515</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>37.08316730221545</v>
+        <v>51.49624183750426</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>35.83638634270621</v>
+        <v>49.59809750287723</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>34.64850146861852</v>
+        <v>47.79108352579985</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>33.51643086506038</v>
+        <v>46.0703857041041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
-      </c>
-      <c r="B9" s="53" t="n">
-        <v>43.3092625424965</v>
+        <v>20.9</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>59.88880666812968</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>41.76922114250189</v>
+        <v>57.5891974439696</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>40.30331725125443</v>
+        <v>55.40182891834385</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>38.90760711680897</v>
+        <v>53.32068165209778</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>37.57837509715824</v>
+        <v>51.34008625732926</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>36.31211945054021</v>
+        <v>49.45470150772154</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>35.10553907253427</v>
+        <v>47.65949391157799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
-      </c>
-      <c r="B10" s="53" t="n">
-        <v>45.40793901409563</v>
-      </c>
-      <c r="C10" s="53" t="n">
-        <v>43.77174978825729</v>
+        <v>21.9</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>61.98748313972882</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>59.59172608972499</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>42.21452125974676</v>
+        <v>57.31303292683617</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>40.73204693140249</v>
+        <v>55.14512146669131</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>39.32036385161027</v>
+        <v>53.0820750117813</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>37.9757374324619</v>
+        <v>51.11831948964323</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>36.69464728000816</v>
+        <v>49.24860211905187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="B11" s="53" t="n">
-        <v>47.50661548569478</v>
-      </c>
-      <c r="C11" s="53" t="n">
-        <v>45.7742784340127</v>
-      </c>
-      <c r="D11" s="53" t="n">
-        <v>44.12572526823909</v>
+        <v>22.9</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>64.08615961132796</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>61.5942547354804</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>59.22423693532851</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>42.55648674599601</v>
+        <v>56.96956128128483</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>41.0623526060623</v>
+        <v>54.82406376623332</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>39.63935541438359</v>
+        <v>52.78193747156492</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>38.28375548748204</v>
+        <v>50.83771032652576</v>
       </c>
     </row>
     <row r="13">
@@ -1332,7 +1332,7 @@
         <v>0.07868665825586801</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>19.9</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.6077822244202611</v>
+        <v>0.5781904679867597</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24395,7 +24395,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="46">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>37.08316730221545</v>
+        <v>51.49624183750426</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>55.10242524861258</v>
+        <v>75.47019339068979</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>24.526834133011</v>
+        <v>34.35521961956263</v>
       </c>
     </row>
     <row r="59">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24824,7 +24824,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24832,7 +24832,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24851,7 +24855,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24859,7 +24863,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24878,7 +24886,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24886,7 +24894,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24905,7 +24917,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24913,7 +24925,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24932,7 +24948,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24940,7 +24956,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24959,7 +24979,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24967,7 +24987,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24986,7 +25010,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24994,7 +25018,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25013,7 +25041,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -25021,7 +25049,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25040,7 +25072,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25048,7 +25080,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25067,7 +25103,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25075,7 +25111,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25094,7 +25134,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25102,7 +25142,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25121,7 +25165,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25129,7 +25173,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25148,7 +25196,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25156,7 +25204,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25175,7 +25227,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25183,7 +25235,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25202,12 +25258,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.9x</t>
         </is>
       </c>
       <c r="F22" s="31" t="inlineStr"/>
@@ -25229,7 +25285,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -25237,7 +25293,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr"/>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25256,7 +25316,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/dcf/ESTC.xlsx
+++ b/dcf/ESTC.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06368665825586801</v>
+        <v>0.06384868400658288</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.06868665825586802</v>
+        <v>0.06884868400658288</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07368665825586801</v>
+        <v>0.07384868400658287</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.07868665825586801</v>
+        <v>0.07884868400658288</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08368665825586802</v>
+        <v>0.08384868400658288</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.08868665825586801</v>
+        <v>0.08884868400658287</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09368665825586801</v>
+        <v>0.09384868400658287</v>
       </c>
     </row>
     <row r="5">
@@ -1135,25 +1135,25 @@
         <v>16.9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>51.49410078173313</v>
+        <v>46.36063057947891</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>49.57908286094796</v>
+        <v>44.67317937942608</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>47.75701288437452</v>
+        <v>43.06747238641479</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>46.0229223937237</v>
+        <v>41.53914424499204</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>44.37213123952115</v>
+        <v>40.08408276312378</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>42.80022958003478</v>
+        <v>38.69841311195325</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>41.30306108168243</v>
+        <v>37.37848307981342</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>17.9</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>53.59277725333227</v>
+        <v>48.20275816227769</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>51.58161150670337</v>
+        <v>46.43092507752596</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>49.66821689286684</v>
+        <v>44.74506853283884</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>47.84736220831721</v>
+        <v>43.14059264855523</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>46.11411999397318</v>
+        <v>41.61316824915816</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>44.46384756195648</v>
+        <v>40.15871621035023</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>42.89216928915631</v>
+        <v>38.77339191765506</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>18.9</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>55.69145372493141</v>
+        <v>50.04488574507648</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>53.58414015245878</v>
+        <v>48.18867077562583</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>51.57942090135918</v>
+        <v>46.42266467926288</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>49.67180202291074</v>
+        <v>44.74204105211842</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>47.85610874842521</v>
+        <v>43.14225373519253</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>46.12746554387817</v>
+        <v>41.61901930874719</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>44.48127749663021</v>
+        <v>40.1683007554967</v>
       </c>
     </row>
     <row r="8">
@@ -1213,103 +1213,103 @@
         <v>19.9</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>57.79013019653055</v>
+        <v>51.88701332787527</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>55.58666879821419</v>
+        <v>49.94641647372571</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>53.4906249098515</v>
+        <v>48.10026082568693</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>51.49624183750426</v>
+        <v>46.34348945568161</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>49.59809750287723</v>
+        <v>44.67133922122691</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>47.79108352579985</v>
+        <v>43.07932240714416</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>46.0703857041041</v>
+        <v>41.56320959333834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>20.9</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>59.88880666812968</v>
+      <c r="B9" s="53" t="n">
+        <v>53.72914091067404</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>57.5891974439696</v>
+        <v>51.70416217182559</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>55.40182891834385</v>
+        <v>49.77785697211097</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>53.32068165209778</v>
+        <v>47.9449378592448</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>51.34008625732926</v>
+        <v>46.20042470726128</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>49.45470150772154</v>
+        <v>44.53962550554114</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>47.65949391157799</v>
+        <v>42.95811843117998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>21.9</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>61.98748313972882</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>59.59172608972499</v>
+      <c r="B10" s="53" t="n">
+        <v>55.57126849347283</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>53.46190786992546</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>57.31303292683617</v>
+        <v>51.45545311853502</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>55.14512146669131</v>
+        <v>49.54638626280799</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>53.0820750117813</v>
+        <v>47.72951019329566</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>51.11831948964323</v>
+        <v>45.99992860393812</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>49.24860211905187</v>
+        <v>44.35302726902163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
         <v>22.9</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>64.08615961132796</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>61.5942547354804</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>59.22423693532851</v>
+      <c r="B11" s="53" t="n">
+        <v>57.41339607627162</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>55.21965356802534</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>53.13304926495907</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>56.96956128128483</v>
+        <v>51.14783466637117</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>54.82406376623332</v>
+        <v>49.25859567933002</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>52.78193747156492</v>
+        <v>47.46023170233508</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>50.83771032652576</v>
+        <v>45.74793610686326</v>
       </c>
     </row>
     <row r="13">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>58.04000091552734</v>
+        <v>60.625</v>
       </c>
     </row>
     <row r="14">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.07868665825586801</v>
+        <v>0.07884868400658288</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>19.9</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.5781904679867597</v>
+        <v>0.5842460035909083</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>58.04000091552734</v>
+        <v>60.625</v>
       </c>
     </row>
     <row r="49">
@@ -24440,7 +24440,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>51.49624183750426</v>
+        <v>46.34348945568161</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>75.47019339068979</v>
+        <v>66.14341453380707</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>34.35521961956263</v>
+        <v>31.76170363276636</v>
       </c>
     </row>
     <row r="59">
